--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.26547716177846</v>
+        <v>10.443140038789</v>
       </c>
       <c r="D2" t="n">
-        <v>64.30291701803638</v>
+        <v>10.44922401543091</v>
       </c>
       <c r="E2" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.64470521958783</v>
+        <v>7.417264598183023</v>
       </c>
       <c r="D3" t="n">
-        <v>45.52980109041646</v>
+        <v>7.398592677192674</v>
       </c>
       <c r="E3" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F3" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.23969166216549</v>
+        <v>4.263949895101892</v>
       </c>
       <c r="D4" t="n">
-        <v>26.40047978721195</v>
+        <v>4.290077965421943</v>
       </c>
       <c r="E4" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.21691480484279</v>
+        <v>5.885248655786954</v>
       </c>
       <c r="D5" t="n">
-        <v>36.37967649545989</v>
+        <v>5.911697430512232</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F5" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.03670800807021</v>
+        <v>5.368465051311409</v>
       </c>
       <c r="D6" t="n">
-        <v>32.93514353462624</v>
+        <v>5.351960824376764</v>
       </c>
       <c r="E6" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F6" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.13995783450814</v>
+        <v>8.635243148107573</v>
       </c>
       <c r="D7" t="n">
-        <v>53.1620504434141</v>
+        <v>8.638833197054792</v>
       </c>
       <c r="E7" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F7" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.04330990460136</v>
+        <v>10.24453785949772</v>
       </c>
       <c r="D8" t="n">
-        <v>62.95421885750331</v>
+        <v>10.23006056434429</v>
       </c>
       <c r="E8" t="n">
-        <v>13.78098268699951</v>
+        <v>2.23940968663742</v>
       </c>
       <c r="F8" t="n">
-        <v>13.7390192669955</v>
+        <v>2.23259063088677</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
